--- a/manual_qwen_compare.xlsx
+++ b/manual_qwen_compare.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Human-MME\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9CC3C303-3BA2-4EB0-B441-943C006871B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4875B4A-6365-4724-B7B8-6475592D7E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2445" yWindow="9000" windowWidth="23010" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6315" yWindow="1920" windowWidth="23010" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual vs Qwen" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
   <si>
     <t>The woman eats a cream cake and thoroughly enjoys the sweetness.</t>
   </si>
@@ -95,22 +95,10 @@
     <t>A surge of triumph and exhilaration floods through with a release of pent-up energy and excitement marking a significant achievement after prolonged effort followed by deep relief and profound satisfaction intertwined with a sense of accomplishment and elation</t>
   </si>
   <si>
-    <t>A man and woman who are attracted to each other share food from the same skewer; the atmosphere is filled with flirtation, and they are both happy.</t>
-  </si>
-  <si>
-    <t>A deep sense of determination fuels a profound resolve driven by duty and commitment to a greater cause despite overwhelming fear and the weight of potential risk</t>
-  </si>
-  <si>
     <t>A group of good friends are happily taking selfies on a boat, enjoying this joyful moment together.</t>
   </si>
   <si>
     <t>Joy and excitement are dominant with a strong undercurrent of pride and satisfaction accompanied by a deep sense of connection and appreciation for the moment and surroundings</t>
-  </si>
-  <si>
-    <t>The woman stands in the kitchen holding a fruit knife with a fierce expression and wide eyes, emotionally agitated.</t>
-  </si>
-  <si>
-    <t>Determination fuels focus while subtle tension reveals underlying frustration yet persistence remains unwavering in the face of challenge</t>
   </si>
   <si>
     <t>Facing his ruined book, the man covers his face with his hands, full of regret.</t>
@@ -831,6 +819,14 @@
   </si>
   <si>
     <t>Similarity Score</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>The woman stands in the kitchen holding a fruit knife with a fierce expression and wide eyes, emotionally agitated.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Determination fuels focus while subtle tension reveals underlying frustration yet persistence remains unwavering in the face of challenge</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1154,7 +1150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="情绪emotion"/>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr defaultColWidth="14.21875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="77.77734375" customWidth="1"/>
@@ -1164,13 +1160,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5">
@@ -1291,81 +1287,81 @@
         <v>21</v>
       </c>
       <c r="C12" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>262</v>
       </c>
       <c r="C13" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5">
       <c r="A15" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16.5">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.5">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16.5">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19" s="1">
         <v>8</v>
@@ -1373,21 +1369,21 @@
     </row>
     <row r="20" spans="1:3" ht="16.5">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.5">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="1">
         <v>10</v>
@@ -1395,65 +1391,65 @@
     </row>
     <row r="22" spans="1:3" ht="16.5">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.5">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.5">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16.5">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16.5">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C26" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16.5">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C27" s="1">
         <v>9</v>
@@ -1461,43 +1457,43 @@
     </row>
     <row r="28" spans="1:3" ht="16.5">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16.5">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16.5">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C30" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16.5">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C31" s="1">
         <v>8</v>
@@ -1505,21 +1501,21 @@
     </row>
     <row r="32" spans="1:3" ht="16.5">
       <c r="A32" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C32" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16.5">
       <c r="A33" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C33" s="1">
         <v>9</v>
@@ -1527,21 +1523,21 @@
     </row>
     <row r="34" spans="1:3" ht="16.5">
       <c r="A34" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C34" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16.5">
       <c r="A35" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -1549,10 +1545,10 @@
     </row>
     <row r="36" spans="1:3" ht="16.5">
       <c r="A36" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C36" s="1">
         <v>10</v>
@@ -1560,65 +1556,65 @@
     </row>
     <row r="37" spans="1:3" ht="16.5">
       <c r="A37" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C37" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16.5">
       <c r="A38" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C38" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16.5">
       <c r="A39" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C39" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16.5">
       <c r="A40" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C40" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16.5">
       <c r="A41" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16.5">
       <c r="A42" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C42" s="1">
         <v>9</v>
@@ -1626,10 +1622,10 @@
     </row>
     <row r="43" spans="1:3" ht="16.5">
       <c r="A43" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C43" s="1">
         <v>9</v>
@@ -1637,242 +1633,241 @@
     </row>
     <row r="44" spans="1:3" ht="16.5">
       <c r="A44" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C44" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16.5">
       <c r="A45" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C45" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16.5">
       <c r="A46" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16.5">
       <c r="A47" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C47" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16.5">
       <c r="A48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="16.5">
+      <c r="A49" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="16.5">
-      <c r="A49" s="2" t="s">
+      <c r="C49" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="16.5">
+      <c r="A50" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="16.5">
-      <c r="A50" s="2" t="s">
+      <c r="C50" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="16.5">
+      <c r="A51" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C50" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="16.5">
-      <c r="A51" s="2" t="s">
+      <c r="C51" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="16.5">
+      <c r="A52" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="16.5">
-      <c r="A52" s="2" t="s">
+      <c r="C52" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="16.5">
+      <c r="A53" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="16.5">
-      <c r="A53" s="2" t="s">
+      <c r="C53" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="16.5">
+      <c r="A54" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C53" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="16.5">
-      <c r="A54" s="2" t="s">
+      <c r="C54" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="16.5">
+      <c r="A55" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="16.5">
-      <c r="A55" s="2" t="s">
+      <c r="C55" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="16.5">
+      <c r="A56" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="16.5">
-      <c r="A56" s="2" t="s">
+      <c r="C56" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="16.5">
+      <c r="A57" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C56" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="16.5">
-      <c r="A57" s="2" t="s">
+      <c r="C57" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="16.5">
+      <c r="A58" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C57" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="16.5">
-      <c r="A58" s="2" t="s">
+      <c r="C58" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="16.5">
+      <c r="A59" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C58" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="16.5">
-      <c r="A59" s="2" t="s">
+      <c r="C59" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="16.5">
+      <c r="A60" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C59" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="16.5">
-      <c r="A60" s="2" t="s">
+      <c r="C60" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="16.5">
+      <c r="A61" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C60" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="16.5">
-      <c r="A61" s="2" t="s">
+      <c r="C61" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="16.5">
+      <c r="A62" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C61" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="16.5">
-      <c r="A62" s="2" t="s">
+      <c r="C62" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="16.5">
+      <c r="A63" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C62" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="16.5">
-      <c r="A63" s="2" t="s">
+      <c r="C63" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="18" customHeight="1">
+      <c r="A64" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="16.5">
-      <c r="A64" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="C64" s="1">
-        <v>10</v>
-      </c>
-      <c r="D64" s="1"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="65" spans="1:3" ht="18" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C65" s="1">
         <v>8</v>
@@ -1880,98 +1875,98 @@
     </row>
     <row r="66" spans="1:3" ht="18" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C66" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="18" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C67" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="18" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C68" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="18" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C69" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="18" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C70" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="18" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C71" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="18" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C72" s="1">
+        <v>139</v>
+      </c>
+      <c r="C72" s="3">
         <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="18" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C73" s="3">
+        <v>141</v>
+      </c>
+      <c r="C73" s="1">
         <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="18" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C74" s="1">
         <v>10</v>
@@ -1979,10 +1974,10 @@
     </row>
     <row r="75" spans="1:3" ht="18" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C75" s="1">
         <v>10</v>
@@ -1990,10 +1985,10 @@
     </row>
     <row r="76" spans="1:3" ht="18" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C76" s="1">
         <v>10</v>
@@ -2001,10 +1996,10 @@
     </row>
     <row r="77" spans="1:3" ht="18" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C77" s="1">
         <v>10</v>
@@ -2012,10 +2007,10 @@
     </row>
     <row r="78" spans="1:3" ht="18" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C78" s="1">
         <v>10</v>
@@ -2023,10 +2018,10 @@
     </row>
     <row r="79" spans="1:3" ht="18" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C79" s="1">
         <v>10</v>
@@ -2034,21 +2029,21 @@
     </row>
     <row r="80" spans="1:3" ht="18" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C80" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="18" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C81" s="1">
         <v>8</v>
@@ -2056,21 +2051,21 @@
     </row>
     <row r="82" spans="1:3" ht="18" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C82" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="18" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C83" s="1">
         <v>6</v>
@@ -2078,21 +2073,21 @@
     </row>
     <row r="84" spans="1:3" ht="18" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C84" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="18" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C85" s="1">
         <v>9</v>
@@ -2100,87 +2095,87 @@
     </row>
     <row r="86" spans="1:3" ht="18" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C86" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="18" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C87" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="18" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C88" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="18" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C89" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="18" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C90" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="18" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C91" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="18" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C92" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="18" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C93" s="1">
         <v>8</v>
@@ -2188,32 +2183,32 @@
     </row>
     <row r="94" spans="1:3" ht="18" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C94" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="18" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C95" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="18" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C96" s="1">
         <v>9</v>
@@ -2221,54 +2216,54 @@
     </row>
     <row r="97" spans="1:3" ht="18" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C97" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="18" customHeight="1">
       <c r="A98" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C98" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="18" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C99" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="18" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C100" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="18" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C101" s="1">
         <v>9</v>
@@ -2276,120 +2271,120 @@
     </row>
     <row r="102" spans="1:3" ht="18" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C102" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="18" customHeight="1">
       <c r="A103" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C103" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="18" customHeight="1">
       <c r="A104" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C104" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="18" customHeight="1">
       <c r="A105" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C105" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="18" customHeight="1">
       <c r="A106" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C106" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="18" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C107" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="18" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C108" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="18" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C109" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="18" customHeight="1">
       <c r="A110" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C110" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="18" customHeight="1">
       <c r="A111" s="2" t="s">
-        <v>218</v>
+        <v>257</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C111" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="18" customHeight="1">
       <c r="A112" s="2" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C112" s="1">
         <v>7</v>
@@ -2397,32 +2392,32 @@
     </row>
     <row r="113" spans="1:3" ht="18" customHeight="1">
       <c r="A113" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C113" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="18" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C114" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="18" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C115" s="1">
         <v>10</v>
@@ -2430,43 +2425,43 @@
     </row>
     <row r="116" spans="1:3" ht="18" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C116" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="18" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C117" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="18" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C118" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="18" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C119" s="1">
         <v>10</v>
@@ -2474,43 +2469,43 @@
     </row>
     <row r="120" spans="1:3" ht="18" customHeight="1">
       <c r="A120" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C120" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="18" customHeight="1">
       <c r="A121" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C121" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="18" customHeight="1">
       <c r="A122" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C122" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="18" customHeight="1">
       <c r="A123" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C123" s="1">
         <v>10</v>
@@ -2518,43 +2513,43 @@
     </row>
     <row r="124" spans="1:3" ht="18" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C124" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="18" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C125" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="18" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C126" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="18" customHeight="1">
       <c r="A127" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C127" s="1">
         <v>10</v>
@@ -2562,64 +2557,54 @@
     </row>
     <row r="128" spans="1:3" ht="18" customHeight="1">
       <c r="A128" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C128" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="18" customHeight="1">
+      <c r="A129" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B129" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C128" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="18" customHeight="1">
-      <c r="A129" s="2" t="s">
+      <c r="C129" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="18" customHeight="1">
+      <c r="A130" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B130" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C129" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="18" customHeight="1">
-      <c r="A130" s="2" t="s">
+      <c r="C130" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="18" customHeight="1">
+      <c r="A131" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B131" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C130" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="18" customHeight="1">
-      <c r="A131" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="C131" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="18" customHeight="1">
-      <c r="A132" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>260</v>
-      </c>
+    <row r="132" spans="1:4" ht="18" customHeight="1">
       <c r="C132" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="18" customHeight="1">
-      <c r="C133" s="1">
-        <f>AVERAGE(C2:C132)</f>
-        <v>8.7099236641221367</v>
-      </c>
+        <f>AVERAGE(C2:C131)</f>
+        <v>8.7538461538461547</v>
+      </c>
+      <c r="D132" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
